--- a/content/post/drafts/weekly-picks/2025TdS/fantasy-team.xlsx
+++ b/content/post/drafts/weekly-picks/2025TdS/fantasy-team.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Skier</t>
   </si>
@@ -38,112 +38,103 @@
     <t xml:space="preserve">Norway</t>
   </si>
   <si>
-    <t xml:space="preserve">300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Astrid Øyre Slind</t>
-  </si>
-  <si>
-    <t xml:space="preserve">246</t>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heidi Weng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jessie Diggins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sophia Laukli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kerttu Niskanen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nora Sanness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teresa Stadlober</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Austria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
   </si>
   <si>
     <t xml:space="preserve">Krista Pärmäkoski</t>
   </si>
   <si>
-    <t xml:space="preserve">Finland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victoria Carl</t>
+    <t xml:space="preserve">Simen Hegstad Krüger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friedrich Moch</t>
   </si>
   <si>
     <t xml:space="preserve">Germany</t>
   </si>
   <si>
-    <t xml:space="preserve">218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teresa Stadlober</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Austria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katharina Hennig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johanna Matintalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sofia Henriksson</t>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andreas Fjorden Ree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Johannes Høsflot Klæbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mika Vermeulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hugo Lapalus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iver Tildheim Andersen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jens Burman</t>
   </si>
   <si>
     <t xml:space="preserve">Sweden</t>
   </si>
   <si>
-    <t xml:space="preserve">143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martin Løwstrøm Nyenget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Johannes Høsflot Klæbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iivo Niskanen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Simen Hegstad Krüger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Friedrich Moch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hugo Lapalus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andreas Fjorden Ree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jens Burman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">199</t>
+    <t xml:space="preserve">29</t>
   </si>
 </sst>
 </file>
@@ -517,7 +508,7 @@
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>5079</v>
+        <v>8504</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -534,7 +525,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>3581</v>
+        <v>14808</v>
       </c>
       <c r="E4" t="s">
         <v>13</v>
@@ -548,61 +539,61 @@
         <v>6</v>
       </c>
       <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2689</v>
+      </c>
+      <c r="E5" t="s">
         <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>10644</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
         <v>6</v>
       </c>
       <c r="C6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6230</v>
+      </c>
+      <c r="E6" t="s">
         <v>18</v>
-      </c>
-      <c r="D6" t="n">
-        <v>4457</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>6711</v>
+        <v>1975</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>1995</v>
+        <v>4457</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -616,44 +607,44 @@
         <v>6</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D9" t="n">
-        <v>226</v>
+        <v>3581</v>
       </c>
       <c r="E9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>9387</v>
+        <v>7021</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
       <c r="D11" t="n">
-        <v>16209</v>
+        <v>3962</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
@@ -664,101 +655,101 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>7207</v>
+        <v>5755</v>
       </c>
       <c r="E12" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>7021</v>
+        <v>16209</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>3962</v>
+        <v>5810</v>
       </c>
       <c r="E14" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
         <v>3313</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>5755</v>
+        <v>1114</v>
       </c>
       <c r="E16" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C17" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>1628</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
